--- a/sampleprojects/TaxReturn/excel/states/IN.xlsx
+++ b/sampleprojects/TaxReturn/excel/states/IN.xlsx
@@ -72,7 +72,7 @@
     <t>Compute IN exemptions, taxable income, and flat tax</t>
   </si>
   <si>
-    <t>set result.in_total_exemptions = length of job.taxpayers * in_personal_exemption + length of job.dependents * in_dependent_exemption; set result.in_taxable_income = the maximum of (result.agi - result.in_total_exemptions) and 0.0; set result.in_state_tax = result.in_taxable_income * in_tax_rate; add "  IN exemptions: $" + result.in_total_exemptions to job.audit_trail; add "  IN state tax (3.00%): $" + result.in_state_tax to job.audit_trail</t>
+    <t>set result.in_total_exemptions = length of job.taxpayers * in_personal_exemption + length of job.dependents * in_dependent_exemption; set result.in_taxable_income = the maximum of (result.state_calc_agi - result.in_total_exemptions) and 0.0; set result.in_state_tax = result.in_taxable_income * in_tax_rate; add "  IN exemptions: $" + result.in_total_exemptions to job.audit_trail; add "  IN state tax (3.00%): $" + result.in_state_tax to job.audit_trail</t>
   </si>
   <si>
     <t>X</t>
